--- a/results/log_pv_cap_per_inst/log_pv_cap_per_inst_densities_adensity_effects.xlsx
+++ b/results/log_pv_cap_per_inst/log_pv_cap_per_inst_densities_adensity_effects.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>adensity</t>
+          <t>D(Firm assets)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -521,39 +521,39 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>-0.000</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>-0.000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>0.000</t>
@@ -561,17 +561,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,291 +608,291 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1.647</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.005</t>
+          <t>-0.176</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1.824</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>-0.052</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1.426</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1.312</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1.151</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1.004</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.117</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.887</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1.182</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.599</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.583</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1.194</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.766</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.428</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>4.460</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4.459</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.178</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>-0.000</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.065</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.190</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.009</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>-0.002</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>-0.001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.080</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.146</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.226</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.067</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>-0.151</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.237</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.009</t>
+          <t>-0.428</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-0.008</t>
+          <t>-0.378</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>-0.073</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.037</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.036</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.039</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.025</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>-0.014</t>
         </is>
       </c>
     </row>
